--- a/ToxCast_model/experiments/example/prediction_input_template.xlsx
+++ b/ToxCast_model/experiments/example/prediction_input_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>assay_name</t>
   </si>
@@ -506,9 +506,15 @@
       <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="E1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="2" t="s">
